--- a/etf_holdings/2026-10-06_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:23</t>
+          <t>2026-10-06 01:24:28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:23</t>
+          <t>2026-10-06 01:24:28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:23</t>
+          <t>2026-10-06 01:24:28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:23</t>
+          <t>2026-10-06 01:24:28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:23</t>
+          <t>2026-10-06 01:24:28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:23</t>
+          <t>2026-10-06 01:24:28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:23</t>
+          <t>2026-10-06 01:24:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:23</t>
+          <t>2026-10-06 01:24:28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:23</t>
+          <t>2026-10-06 01:24:28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:23</t>
+          <t>2026-10-06 01:24:28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:23</t>
+          <t>2026-10-06 01:24:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:23</t>
+          <t>2026-10-06 01:24:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:23</t>
+          <t>2026-10-06 01:24:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:23</t>
+          <t>2026-10-06 01:24:28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:23</t>
+          <t>2026-10-06 01:24:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:24</t>
+          <t>2026-10-06 01:24:29</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:24</t>
+          <t>2026-10-06 01:24:29</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:24</t>
+          <t>2026-10-06 01:24:29</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:24</t>
+          <t>2026-10-06 01:24:29</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:24</t>
+          <t>2026-10-06 01:24:29</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:24</t>
+          <t>2026-10-06 01:24:29</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:24</t>
+          <t>2026-10-06 01:24:29</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:24</t>
+          <t>2026-10-06 01:24:29</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:24</t>
+          <t>2026-10-06 01:24:29</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:24</t>
+          <t>2026-10-06 01:24:29</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:24</t>
+          <t>2026-10-06 01:24:29</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:24</t>
+          <t>2026-10-06 01:24:29</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:24</t>
+          <t>2026-10-06 01:24:29</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:24</t>
+          <t>2026-10-06 01:24:29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:24</t>
+          <t>2026-10-06 01:24:29</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:25</t>
+          <t>2026-10-06 01:24:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:25</t>
+          <t>2026-10-06 01:24:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:25</t>
+          <t>2026-10-06 01:24:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:25</t>
+          <t>2026-10-06 01:24:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:25</t>
+          <t>2026-10-06 01:24:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:25</t>
+          <t>2026-10-06 01:24:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:25</t>
+          <t>2026-10-06 01:24:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:25</t>
+          <t>2026-10-06 01:24:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:25</t>
+          <t>2026-10-06 01:24:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:25</t>
+          <t>2026-10-06 01:24:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:25</t>
+          <t>2026-10-06 01:24:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:25</t>
+          <t>2026-10-06 01:24:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">

--- a/etf_holdings/2026-10-06_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:28</t>
+          <t>2026-10-06 02:27:59</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:29</t>
+          <t>2026-10-06 02:28:01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:30</t>
+          <t>2026-10-06 02:28:02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:30</t>
+          <t>2026-10-06 02:28:02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:30</t>
+          <t>2026-10-06 02:28:02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:30</t>
+          <t>2026-10-06 02:28:02</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:30</t>
+          <t>2026-10-06 02:28:02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:30</t>
+          <t>2026-10-06 02:28:02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:30</t>
+          <t>2026-10-06 02:28:02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:30</t>
+          <t>2026-10-06 02:28:02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:30</t>
+          <t>2026-10-06 02:28:02</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:30</t>
+          <t>2026-10-06 02:28:02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:30</t>
+          <t>2026-10-06 02:28:02</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 01:24:30</t>
+          <t>2026-10-06 02:28:02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">

--- a/etf_holdings/2026-10-06_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:59</t>
+          <t>2026-10-06 19:17:05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.53%1325</t>
+          <t>-1.13%1310</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1325</v>
+        <v>1310</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.50%2,482,000</t>
+          <t>7.30%2,482,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.50%</t>
+          <t>7.30%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:59</t>
+          <t>2026-10-06 19:17:05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+4.22%3585</t>
+          <t>+2.79%3685</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+4.22%</t>
+          <t>+2.79%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3585</v>
+        <v>3685</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.93%871,000</t>
+          <t>6.94%871,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>6.94%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:59</t>
+          <t>2026-10-06 19:17:05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-2.17%2485</t>
+          <t>-6.44%2325</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2.17%</t>
+          <t>-6.44%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2485</v>
+        <v>2325</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.82%1,161,000</t>
+          <t>6.41%1,161,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.82%</t>
+          <t>6.41%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:59</t>
+          <t>2026-10-06 19:17:05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+3%2575</t>
+          <t>+0.39%2585</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+3%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2575</v>
+        <v>2585</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.46%1,116,000</t>
+          <t>6.38%1,116,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.46%</t>
+          <t>6.38%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:59</t>
+          <t>2026-10-06 19:17:05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+5.63%1595</t>
+          <t>+5.18%5995</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+5.63%</t>
+          <t>+5.18%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1595</v>
+        <v>5995</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.70%1,630,000</t>
+          <t>5.89%465,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.70%</t>
+          <t>5.89%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1630000</v>
+        <v>465000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:59</t>
+          <t>2026-10-06 19:17:05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+9.93%5700</t>
+          <t>+0.31%1600</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+9.93%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5700</v>
+        <v>1600</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.58%465,000</t>
+          <t>5.77%1,630,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.58%</t>
+          <t>5.77%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>465000</v>
+        <v>1630000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:59</t>
+          <t>2026-10-06 19:17:05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+5.6%2075</t>
+          <t>-1.2%2050</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+5.6%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2075</v>
+        <v>2050</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.47%1,204,000</t>
+          <t>5.55%1,204,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.47%</t>
+          <t>5.55%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:59</t>
+          <t>2026-10-06 19:17:05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+9.96%13355</t>
+          <t>-1.91%13100</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>13355</v>
+        <v>13100</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.78%170,000</t>
+          <t>5.04%170,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.78%</t>
+          <t>5.04%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:59</t>
+          <t>2026-10-06 19:17:05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+7%6730</t>
+          <t>+1.86%6855</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+7%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6730</v>
+        <v>6855</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.26%293,000</t>
+          <t>4.38%293,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>4.38%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:59</t>
+          <t>2026-10-06 19:17:05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+3.95%5520</t>
+          <t>+2.72%5670</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+3.95%</t>
+          <t>+2.72%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5520</v>
+        <v>5670</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.23%344,000</t>
+          <t>4.22%344,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.23%</t>
+          <t>4.22%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:59</t>
+          <t>2026-10-06 19:17:05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+1.27%560</t>
+          <t>0%561</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+1.27%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.43%2,682,000</t>
+          <t>3.34%2,682,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.34%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:59</t>
+          <t>2026-10-06 19:17:05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>1815富喬</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+2.4%1495</t>
+          <t>-1.17%127</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1495</v>
+        <v>127</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.27%968,000</t>
+          <t>3.26%11,420,868</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.27%</t>
+          <t>3.26%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>968000</v>
+        <v>11420868</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:59</t>
+          <t>2026-10-06 19:17:05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1815富喬</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+6.2%128.5</t>
+          <t>+0.67%1505</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+6.2%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>128.5</v>
+        <v>1505</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.20%11,420,868</t>
+          <t>3.21%968,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>11420868</v>
+        <v>968000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:59</t>
+          <t>2026-10-06 19:17:05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,25 +1297,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+1.61%189.5</t>
+          <t>-2.62%8375</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+1.61%</t>
+          <t>-2.62%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>189.5</v>
+        <v>8375</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.13%7,245,000</t>
+          <t>3.13%164,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1324,11 +1324,11 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>7245000</v>
+        <v>164000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:59</t>
+          <t>2026-10-06 19:17:05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+8.86%8600</t>
+          <t>0%189.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+8.86%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>8600</v>
+        <v>189.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.00%164,000</t>
+          <t>3.05%7,245,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>3.05%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>164000</v>
+        <v>7245000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:01</t>
+          <t>2026-10-06 19:17:06</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6584南俊國際</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+1.88%541</t>
+          <t>+2.45%293</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+1.88%</t>
+          <t>+2.45%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>541</v>
+        <v>293</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.60%2,115,000</t>
+          <t>2.32%3,645,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>2115000</v>
+        <v>3645000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:01</t>
+          <t>2026-10-06 19:17:06</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>6584南俊國際</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+10%286</t>
+          <t>+1.85%551</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+1.85%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>286</v>
+        <v>551</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.19%3,645,000</t>
+          <t>2.29%1,905,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.29%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>3645000</v>
+        <v>1905000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:01</t>
+          <t>2026-10-06 19:17:06</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+3.12%2150</t>
+          <t>-4.74%4920</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+3.12%</t>
+          <t>-4.74%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2150</v>
+        <v>4920</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.07%429,675</t>
+          <t>2.05%179,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.05%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>429675</v>
+        <v>179000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:01</t>
+          <t>2026-10-06 19:17:06</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,16 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+4.29%1095</t>
+          <t>-2.28%1070</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+4.29%</t>
+          <t>-2.28%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1095</v>
+        <v>1070</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:01</t>
+          <t>2026-10-06 19:17:06</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,25 +1663,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+4.34%5165</t>
+          <t>+6.51%2290</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+4.34%</t>
+          <t>+6.51%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5165</v>
+        <v>2290</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.05%179,000</t>
+          <t>2.05%429,675</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1690,11 +1690,11 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>179000</v>
+        <v>429675</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:01</t>
+          <t>2026-10-06 19:17:06</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+4.48%606</t>
+          <t>+1.08%2350</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+4.48%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>606</v>
+        <v>2350</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.34%1,000,000</t>
+          <t>1.42%275,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1000000</v>
+        <v>275000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:01</t>
+          <t>2026-10-06 19:17:06</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,30 +1785,30 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+2.67%576</t>
+          <t>-6.44%567</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+2.67%</t>
+          <t>-6.44%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.30%1,000,000</t>
+          <t>1.35%1,000,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:01</t>
+          <t>2026-10-06 19:17:06</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+6.37%2005</t>
+          <t>-0.35%574</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+6.37%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2005</v>
+        <v>574</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.87%200,000</t>
+          <t>1.28%1,000,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:01</t>
+          <t>2026-10-06 19:17:06</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,34 +1907,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+2.22%6205</t>
+          <t>+2.24%2050</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+2.22%</t>
+          <t>+2.24%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6205</v>
+        <v>2050</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.72%51,000</t>
+          <t>0.89%200,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>51000</v>
+        <v>200000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:01</t>
+          <t>2026-10-06 19:17:06</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+9.96%751</t>
+          <t>-1.21%6130</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>751</v>
+        <v>6130</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.59%373,000</t>
+          <t>0.70%51,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>373000</v>
+        <v>51000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:01</t>
+          <t>2026-10-06 19:17:06</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>8150南茂</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-2.36%124</t>
+          <t>+4.79%787</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-2.36%</t>
+          <t>+4.79%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>124</v>
+        <v>787</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.58%1,957,000</t>
+          <t>0.62%373,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1957000</v>
+        <v>373000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:01</t>
+          <t>2026-10-06 19:17:06</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>8150南茂</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+5.96%7205</t>
+          <t>+2.82%127.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+5.96%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>7205</v>
+        <v>127.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.52%33,000</t>
+          <t>0.54%1,957,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>33000</v>
+        <v>1957000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:01</t>
+          <t>2026-10-06 19:17:06</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,34 +2151,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.16%817</t>
+          <t>-1.73%7080</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.16%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>817</v>
+        <v>7080</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.50%261,000</t>
+          <t>0.53%33,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>261000</v>
+        <v>33000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:01</t>
+          <t>2026-10-06 19:17:06</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+3.61%19520</t>
+          <t>-2.74%18985</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+3.61%</t>
+          <t>-2.74%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>19520</v>
+        <v>18985</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:01</t>
+          <t>2026-10-06 19:17:06</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2404漢唐</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+1.95%1310</t>
+          <t>-2.57%796</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+1.95%</t>
+          <t>-2.57%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1310</v>
+        <v>796</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.46%155,000</t>
+          <t>0.47%261,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>155000</v>
+        <v>261000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:02</t>
+          <t>2026-10-06 19:17:08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,25 +2334,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6139亞翔</t>
+          <t>2404漢唐</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+1.94%790</t>
+          <t>+1.91%1335</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+1.94%</t>
+          <t>+1.91%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>790</v>
+        <v>1335</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.45%250,000</t>
+          <t>0.45%155,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>250000</v>
+        <v>155000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:02</t>
+          <t>2026-10-06 19:17:08</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+4.02%388.5</t>
+          <t>-1.4%1755</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+4.02%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>388.5</v>
+        <v>1755</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.44%508,000</t>
+          <t>0.45%113,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>508000</v>
+        <v>113000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:02</t>
+          <t>2026-10-06 19:17:08</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,25 +2456,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2357華碩</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+3.43%995</t>
+          <t>+3.02%1535</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+3.43%</t>
+          <t>+3.02%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>995</v>
+        <v>1535</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.44%196,000</t>
+          <t>0.44%134,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2483,11 +2483,11 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>196000</v>
+        <v>134000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:02</t>
+          <t>2026-10-06 19:17:08</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>6139亞翔</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+5.86%298</t>
+          <t>+0.63%795</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+5.86%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>298</v>
+        <v>795</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.43%659,000</t>
+          <t>0.44%250,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>659000</v>
+        <v>250000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:02</t>
+          <t>2026-10-06 19:17:08</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+2.56%3000</t>
+          <t>-2.19%380</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+2.56%</t>
+          <t>-2.19%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3000</v>
+        <v>380</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.43%63,000</t>
+          <t>0.44%508,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>63000</v>
+        <v>508000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:02</t>
+          <t>2026-10-06 19:17:08</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+9.88%1780</t>
+          <t>+0.34%299</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+9.88%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1780</v>
+        <v>299</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.42%113,000</t>
+          <t>0.44%659,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>113000</v>
+        <v>659000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:02</t>
+          <t>2026-10-06 19:17:08</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>2357華碩</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+9.96%1490</t>
+          <t>+0.5%1000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>+0.5%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1490</v>
+        <v>1000</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.42%134,000</t>
+          <t>0.43%196,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>134000</v>
+        <v>196000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:02</t>
+          <t>2026-10-06 19:17:08</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+4.07%742</t>
+          <t>-2.67%2920</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+4.07%</t>
+          <t>-2.67%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>742</v>
+        <v>2920</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.41%250,000</t>
+          <t>0.42%63,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>250000</v>
+        <v>63000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:02</t>
+          <t>2026-10-06 19:17:08</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+6.16%2325</t>
+          <t>+0.27%744</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+6.16%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2325</v>
+        <v>744</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.39%76,000</t>
+          <t>0.41%250,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>76000</v>
+        <v>250000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:02</t>
+          <t>2026-10-06 19:17:08</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,25 +2888,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0%1295</t>
+          <t>-2.32%1265</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.32%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1295</v>
+        <v>1265</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.30%99,952</t>
+          <t>0.29%99,952</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:02</t>
+          <t>2026-10-06 19:17:08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-1.6%184</t>
+          <t>+3.8%191</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>+3.8%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.27%629,000</t>
+          <t>0.26%629,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.26%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 02:28:02</t>
+          <t>2026-10-06 19:17:08</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,12 +3010,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+4.12%2530</t>
+          <t>0%2530</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+4.12%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H43" t="n">

--- a/etf_holdings/2026-10-06_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:05</t>
+          <t>2026-10-06 23:19:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:05</t>
+          <t>2026-10-06 23:19:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:05</t>
+          <t>2026-10-06 23:19:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:05</t>
+          <t>2026-10-06 23:19:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:05</t>
+          <t>2026-10-06 23:19:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:05</t>
+          <t>2026-10-06 23:19:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:05</t>
+          <t>2026-10-06 23:19:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:05</t>
+          <t>2026-10-06 23:19:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:05</t>
+          <t>2026-10-06 23:19:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:05</t>
+          <t>2026-10-06 23:19:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:05</t>
+          <t>2026-10-06 23:19:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:05</t>
+          <t>2026-10-06 23:19:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:05</t>
+          <t>2026-10-06 23:19:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:05</t>
+          <t>2026-10-06 23:19:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:05</t>
+          <t>2026-10-06 23:19:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:06</t>
+          <t>2026-10-06 23:19:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:06</t>
+          <t>2026-10-06 23:19:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:06</t>
+          <t>2026-10-06 23:19:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:06</t>
+          <t>2026-10-06 23:19:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:06</t>
+          <t>2026-10-06 23:19:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:06</t>
+          <t>2026-10-06 23:19:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:06</t>
+          <t>2026-10-06 23:19:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:06</t>
+          <t>2026-10-06 23:19:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:06</t>
+          <t>2026-10-06 23:19:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:06</t>
+          <t>2026-10-06 23:19:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:06</t>
+          <t>2026-10-06 23:19:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:06</t>
+          <t>2026-10-06 23:19:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:06</t>
+          <t>2026-10-06 23:19:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:06</t>
+          <t>2026-10-06 23:19:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:06</t>
+          <t>2026-10-06 23:19:41</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:08</t>
+          <t>2026-10-06 23:19:42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:08</t>
+          <t>2026-10-06 23:19:42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:08</t>
+          <t>2026-10-06 23:19:42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:08</t>
+          <t>2026-10-06 23:19:42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:08</t>
+          <t>2026-10-06 23:19:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:08</t>
+          <t>2026-10-06 23:19:42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:08</t>
+          <t>2026-10-06 23:19:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:08</t>
+          <t>2026-10-06 23:19:42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:08</t>
+          <t>2026-10-06 23:19:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:08</t>
+          <t>2026-10-06 23:19:42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:08</t>
+          <t>2026-10-06 23:19:42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 19:17:08</t>
+          <t>2026-10-06 23:19:42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">

--- a/etf_holdings/2026-10-06_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:39</t>
+          <t>2026-10-06 23:28:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:39</t>
+          <t>2026-10-06 23:28:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:39</t>
+          <t>2026-10-06 23:28:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:39</t>
+          <t>2026-10-06 23:28:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:39</t>
+          <t>2026-10-06 23:28:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:39</t>
+          <t>2026-10-06 23:28:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:39</t>
+          <t>2026-10-06 23:28:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:39</t>
+          <t>2026-10-06 23:28:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:39</t>
+          <t>2026-10-06 23:28:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:39</t>
+          <t>2026-10-06 23:28:09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:39</t>
+          <t>2026-10-06 23:28:09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:39</t>
+          <t>2026-10-06 23:28:09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:39</t>
+          <t>2026-10-06 23:28:09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:39</t>
+          <t>2026-10-06 23:28:09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:39</t>
+          <t>2026-10-06 23:28:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:41</t>
+          <t>2026-10-06 23:28:11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:41</t>
+          <t>2026-10-06 23:28:11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:41</t>
+          <t>2026-10-06 23:28:11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:41</t>
+          <t>2026-10-06 23:28:11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:41</t>
+          <t>2026-10-06 23:28:11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:41</t>
+          <t>2026-10-06 23:28:11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:41</t>
+          <t>2026-10-06 23:28:11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:41</t>
+          <t>2026-10-06 23:28:11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:41</t>
+          <t>2026-10-06 23:28:11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:41</t>
+          <t>2026-10-06 23:28:11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:41</t>
+          <t>2026-10-06 23:28:11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:41</t>
+          <t>2026-10-06 23:28:11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:41</t>
+          <t>2026-10-06 23:28:11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:41</t>
+          <t>2026-10-06 23:28:11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:41</t>
+          <t>2026-10-06 23:28:11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:42</t>
+          <t>2026-10-06 23:28:12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:42</t>
+          <t>2026-10-06 23:28:12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:42</t>
+          <t>2026-10-06 23:28:12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:42</t>
+          <t>2026-10-06 23:28:12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:42</t>
+          <t>2026-10-06 23:28:12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:42</t>
+          <t>2026-10-06 23:28:12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:42</t>
+          <t>2026-10-06 23:28:12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:42</t>
+          <t>2026-10-06 23:28:12</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:42</t>
+          <t>2026-10-06 23:28:12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:42</t>
+          <t>2026-10-06 23:28:12</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:42</t>
+          <t>2026-10-06 23:28:12</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 23:19:42</t>
+          <t>2026-10-06 23:28:12</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">

--- a/etf_holdings/2026-10-06_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:09</t>
+          <t>2026-10-06 23:58:44</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:11</t>
+          <t>2026-10-06 23:58:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:12</t>
+          <t>2026-10-06 23:58:46</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:12</t>
+          <t>2026-10-06 23:58:46</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:12</t>
+          <t>2026-10-06 23:58:46</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:12</t>
+          <t>2026-10-06 23:58:46</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:12</t>
+          <t>2026-10-06 23:58:46</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:12</t>
+          <t>2026-10-06 23:58:46</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:12</t>
+          <t>2026-10-06 23:58:46</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:12</t>
+          <t>2026-10-06 23:58:46</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:12</t>
+          <t>2026-10-06 23:58:46</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:12</t>
+          <t>2026-10-06 23:58:46</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:12</t>
+          <t>2026-10-06 23:58:46</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 23:28:12</t>
+          <t>2026-10-06 23:58:46</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
